--- a/erp-server/erp-server-oms/src/main/resources/excel/kolSampleCostError.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/kolSampleCostError.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <r>
       <rPr>
@@ -118,6 +118,21 @@
   </si>
   <si>
     <t>错误数据</t>
+  </si>
+  <si>
+    <t>{.soCode}</t>
+  </si>
+  <si>
+    <t>{.feeType}</t>
+  </si>
+  <si>
+    <t>{.amountStr}</t>
+  </si>
+  <si>
+    <t>{.exchangeRateStr}</t>
+  </si>
+  <si>
+    <t>{.errorMsg}</t>
   </si>
 </sst>
 </file>
@@ -1058,13 +1073,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
     <col min="2" max="2" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="17.75" customWidth="1"/>
-    <col min="4" max="4" width="12.75" customWidth="1"/>
+    <col min="4" max="4" width="24.875" customWidth="1"/>
     <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1085,6 +1100,23 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
